--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimo\OneDrive\デスクトップ\eff_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5089B24D-5ADA-4900-97EC-71304AEAEB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBC1B6E-B0DE-4921-B05F-00FE98E9147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -415,7 +415,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テルヌーラ24</t>
+    <t>ディープビヨンド24</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -582,7 +582,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -640,10 +640,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1403,10 +1409,10 @@
         <v>710</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="L16" s="4">
-        <v>2200</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1429,11 +1435,11 @@
         <f xml:space="preserve"> AVERAGE(I3:I16)</f>
         <v>678.46153846153845</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L17" s="6">
-        <v>2200</v>
+      <c r="K17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="4">
+        <v>530</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1449,6 +1455,12 @@
       <c r="F18" s="4">
         <v>800</v>
       </c>
+      <c r="K18" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" s="4">
+        <v>2400</v>
+      </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
@@ -1462,6 +1474,13 @@
       </c>
       <c r="F19" s="4">
         <v>1050</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="6">
+        <f>AVERAGE(L16:L18)</f>
+        <v>1526.6666666666667</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimo\OneDrive\デスクトップ\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBC1B6E-B0DE-4921-B05F-00FE98E9147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5089B24D-5ADA-4900-97EC-71304AEAEB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -415,7 +415,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ディープビヨンド24</t>
+    <t>テルヌーラ24</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -582,7 +582,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -640,16 +640,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1409,10 +1403,10 @@
         <v>710</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>1650</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1435,11 +1429,11 @@
         <f xml:space="preserve"> AVERAGE(I3:I16)</f>
         <v>678.46153846153845</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" s="4">
-        <v>530</v>
+      <c r="K17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="6">
+        <v>2200</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1455,12 +1449,6 @@
       <c r="F18" s="4">
         <v>800</v>
       </c>
-      <c r="K18" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="4">
-        <v>2400</v>
-      </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
@@ -1474,13 +1462,6 @@
       </c>
       <c r="F19" s="4">
         <v>1050</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" s="6">
-        <f>AVERAGE(L16:L18)</f>
-        <v>1526.6666666666667</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shimo\OneDrive\デスクトップ\eff_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5089B24D-5ADA-4900-97EC-71304AEAEB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173EAC49-A502-41BF-9C2E-5D34A4000F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="88">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -416,6 +416,10 @@
   </si>
   <si>
     <t>テルヌーラ24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プリンセスルーシー24</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -582,7 +586,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -640,10 +644,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1406,7 +1416,7 @@
         <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>2200</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1429,11 +1439,11 @@
         <f xml:space="preserve"> AVERAGE(I3:I16)</f>
         <v>678.46153846153845</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L17" s="6">
-        <v>2200</v>
+      <c r="K17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17" s="4">
+        <v>2400</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.55000000000000004">
@@ -1449,6 +1459,12 @@
       <c r="F18" s="4">
         <v>800</v>
       </c>
+      <c r="K18" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="4">
+        <v>530</v>
+      </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
@@ -1462,6 +1478,13 @@
       </c>
       <c r="F19" s="4">
         <v>1050</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="6">
+        <f>AVERAGE(L16:L18)</f>
+        <v>1526.6666666666667</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173EAC49-A502-41BF-9C2E-5D34A4000F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5613651F-9B42-4046-AA13-0975AD08978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -420,6 +420,87 @@
   </si>
   <si>
     <t>プリンセスルーシー24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクトセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローンリリー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プティフォリー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落札額(万円)</t>
+    <rPh sb="0" eb="3">
+      <t>ラクサツガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レイリオン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンデリング25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リボンフラワー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オリーブティアラ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリノフラッシュ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベルダム25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レディフォグホーン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マリーナドンナ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サトノジュピター26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カレンヒメ26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファディラー26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クイーンズキトゥン26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プリンセサレイク26</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -586,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,12 +729,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D238E629-FE53-4277-BD8E-F46D47DEF395}">
-  <dimension ref="B1:O33"/>
+  <dimension ref="B1:O52"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="4.25" customWidth="1"/>
@@ -1459,7 +1534,7 @@
       <c r="F18" s="4">
         <v>800</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="3" t="s">
         <v>86</v>
       </c>
       <c r="L18" s="4">
@@ -1479,7 +1554,7 @@
       <c r="F19" s="4">
         <v>1050</v>
       </c>
-      <c r="K19" s="22" t="s">
+      <c r="K19" s="5" t="s">
         <v>87</v>
       </c>
       <c r="L19" s="6">
@@ -1629,6 +1704,147 @@
       <c r="C33" s="6">
         <f xml:space="preserve"> AVERAGE(C14:C32)</f>
         <v>5438.8888888888887</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="10"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="3"/>
+      <c r="C36" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="4">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="4">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="4">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="4">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="4">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="4">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="4">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="4">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="4">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="4">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="4">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="6">
+        <f>AVERAGE(C37:C51)</f>
+        <v>12593.333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5613651F-9B42-4046-AA13-0975AD08978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB01000-6A47-47E7-A4E6-0B4719EF4757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="122">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -507,6 +507,82 @@
     <t>平均</t>
     <rPh sb="0" eb="2">
       <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクションセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アヴェクトワ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブルールビー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ショウサンミーベル25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポリアフ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グランデセーヌ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピエーナテーラー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポエティックレガシー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オースミアザレア25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーテサン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラッキーダイス25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナイトドライヴ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラヴァリーノ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠場</t>
+    <rPh sb="0" eb="2">
+      <t>ケツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落札額(万円)</t>
+    <rPh sb="0" eb="3">
+      <t>ラクサツガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マンエン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -667,7 +743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -729,6 +805,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1052,7 +1134,7 @@
     <col min="2" max="2" width="19.4140625" customWidth="1"/>
     <col min="3" max="3" width="11.4140625" customWidth="1"/>
     <col min="4" max="4" width="4.83203125" customWidth="1"/>
-    <col min="5" max="5" width="21.1640625" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.58203125" customWidth="1"/>
     <col min="7" max="7" width="4.4140625" customWidth="1"/>
     <col min="8" max="8" width="19.83203125" customWidth="1"/>
@@ -1648,6 +1730,10 @@
       <c r="C26" s="4">
         <v>7400</v>
       </c>
+      <c r="E26" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
@@ -1656,6 +1742,10 @@
       <c r="C27" s="4">
         <v>4600</v>
       </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
@@ -1664,6 +1754,12 @@
       <c r="C28" s="4">
         <v>1500</v>
       </c>
+      <c r="E28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="4">
+        <v>2700</v>
+      </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
@@ -1672,6 +1768,12 @@
       <c r="C29" s="4">
         <v>14000</v>
       </c>
+      <c r="E29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1700</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
@@ -1680,6 +1782,12 @@
       <c r="C30" s="4">
         <v>5800</v>
       </c>
+      <c r="E30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="4">
+        <v>3500</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
@@ -1688,6 +1796,12 @@
       <c r="C31" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="E31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="4">
+        <v>6000</v>
+      </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
@@ -1696,8 +1810,14 @@
       <c r="C32" s="4">
         <v>3200</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="4">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
@@ -1705,52 +1825,103 @@
         <f xml:space="preserve"> AVERAGE(C14:C32)</f>
         <v>5438.8888888888887</v>
       </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="4">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="4">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C37" s="4">
         <v>20000</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C38" s="4">
         <v>8200</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E38" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="4">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C39" s="4">
         <v>3900</v>
       </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C40" s="4">
         <v>33000</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="E40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="6">
+        <f>AVERAGE(F28:F38)</f>
+        <v>3363.6363636363635</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3" t="s">
         <v>92</v>
       </c>
@@ -1758,7 +1929,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="3" t="s">
         <v>95</v>
       </c>
@@ -1766,7 +1937,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3" t="s">
         <v>96</v>
       </c>
@@ -1774,7 +1945,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
         <v>97</v>
       </c>
@@ -1782,7 +1953,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3" t="s">
         <v>98</v>
       </c>
@@ -1790,7 +1961,7 @@
         <v>39000</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3" t="s">
         <v>99</v>
       </c>
@@ -1798,7 +1969,7 @@
         <v>8600</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="3" t="s">
         <v>100</v>
       </c>
@@ -1806,7 +1977,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
         <v>101</v>
       </c>

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB01000-6A47-47E7-A4E6-0B4719EF4757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D646DEF-FF4C-4017-9D19-04AB3862D6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="152">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -583,6 +583,141 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サマーセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落札額(万円)</t>
+    <rPh sb="0" eb="3">
+      <t>ラクサツガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アドヴェンチャレス25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ココリモアナ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トラディション25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モルトフェリーチェ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リーガルリリー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スウィーテストエンジェル25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドナパフューム25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヤヤラーラ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ムーンフライト25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レッドラフィーネ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アースラブーム25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グリュレーヴ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サラドリーム25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミヤモダイナソー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カルディーン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パワーフレーズ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソートアフター25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルージュアリュール25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キネオダンサー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャンデリアムーン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バトルムーングロウ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プトラナ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブロセリアンド25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミカエリビジン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルージュエクセル25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠場</t>
+    <rPh sb="0" eb="2">
+      <t>ケツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠場</t>
+    <rPh sb="0" eb="2">
+      <t>ケツジョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -743,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -801,16 +936,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1137,7 +1275,7 @@
     <col min="5" max="5" width="21.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.58203125" customWidth="1"/>
     <col min="7" max="7" width="4.4140625" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.75" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
     <col min="10" max="10" width="4.5" customWidth="1"/>
     <col min="11" max="11" width="22.25" customWidth="1"/>
@@ -1519,10 +1657,10 @@
       <c r="I14" s="4">
         <v>1100</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L14" s="20"/>
+      <c r="L14" s="23"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="3" t="s">
@@ -1636,6 +1774,10 @@
       <c r="F19" s="4">
         <v>1050</v>
       </c>
+      <c r="H19" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="13"/>
       <c r="K19" s="5" t="s">
         <v>87</v>
       </c>
@@ -1657,6 +1799,10 @@
       <c r="F20" s="4">
         <v>850</v>
       </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
@@ -1671,6 +1817,12 @@
       <c r="F21" s="4">
         <v>1200</v>
       </c>
+      <c r="H21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="4">
+        <v>2700</v>
+      </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="3" t="s">
@@ -1685,6 +1837,12 @@
       <c r="F22" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="H22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" s="4">
+        <v>600</v>
+      </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="3" t="s">
@@ -1699,6 +1857,12 @@
       <c r="F23" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="H23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="4">
+        <v>5400</v>
+      </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="3" t="s">
@@ -1714,6 +1878,12 @@
         <f xml:space="preserve"> AVERAGE(F4:F21)</f>
         <v>1540.625</v>
       </c>
+      <c r="H24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="3" t="s">
@@ -1722,6 +1892,12 @@
       <c r="C25" s="4">
         <v>1300</v>
       </c>
+      <c r="H25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="4">
+        <v>600</v>
+      </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
@@ -1730,10 +1906,16 @@
       <c r="C26" s="4">
         <v>7400</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="22"/>
+      <c r="F26" s="20"/>
+      <c r="H26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="4">
+        <v>3500</v>
+      </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
@@ -1746,6 +1928,12 @@
       <c r="F27" s="4" t="s">
         <v>121</v>
       </c>
+      <c r="H27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="4">
+        <v>3000</v>
+      </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
@@ -1760,6 +1948,12 @@
       <c r="F28" s="4">
         <v>2700</v>
       </c>
+      <c r="H28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1100</v>
+      </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
@@ -1774,6 +1968,12 @@
       <c r="F29" s="4">
         <v>1700</v>
       </c>
+      <c r="H29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1700</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
@@ -1788,6 +1988,12 @@
       <c r="F30" s="4">
         <v>3500</v>
       </c>
+      <c r="H30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="4">
+        <v>620</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
@@ -1802,6 +2008,12 @@
       <c r="F31" s="4">
         <v>6000</v>
       </c>
+      <c r="H31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2400</v>
+      </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
@@ -1816,8 +2028,14 @@
       <c r="F32" s="4">
         <v>5500</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I32" s="4">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
@@ -1831,16 +2049,28 @@
       <c r="F33" s="4">
         <v>2600</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" s="4">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="E34" s="3" t="s">
         <v>113</v>
       </c>
       <c r="F34" s="4">
         <v>5600</v>
       </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H34" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I34" s="4">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="8" t="s">
         <v>88</v>
       </c>
@@ -1851,8 +2081,14 @@
       <c r="F35" s="4">
         <v>1600</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
         <v>91</v>
@@ -1863,8 +2099,14 @@
       <c r="F36" s="4">
         <v>3200</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I36" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="3" t="s">
         <v>93</v>
       </c>
@@ -1877,8 +2119,14 @@
       <c r="F37" s="4">
         <v>2000</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H37" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="3" t="s">
         <v>94</v>
       </c>
@@ -1891,8 +2139,14 @@
       <c r="F38" s="4">
         <v>2600</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H38" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="3" t="s">
         <v>89</v>
       </c>
@@ -1905,8 +2159,14 @@
       <c r="F39" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="4">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="3" t="s">
         <v>90</v>
       </c>
@@ -1920,56 +2180,99 @@
         <f>AVERAGE(F28:F38)</f>
         <v>3363.6363636363635</v>
       </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H40" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I40" s="4">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C41" s="4">
         <v>8000</v>
       </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H41" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="4">
         <v>12500</v>
       </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H42" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I42" s="4">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C43" s="4">
         <v>5200</v>
       </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I43" s="4">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="4">
         <v>12000</v>
       </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H44" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I44" s="4">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C45" s="4">
         <v>39000</v>
       </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H45" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C46" s="4">
         <v>8600</v>
       </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="H46" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I46" s="6">
+        <f>AVERAGE(I21:I45)</f>
+        <v>2073.913043478261</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="3" t="s">
         <v>100</v>
       </c>
@@ -1977,7 +2280,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
         <v>101</v>
       </c>
